--- a/data/source/weekly/cs-en-us-101pct.xlsx
+++ b/data/source/weekly/cs-en-us-101pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,8 +869,8 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -878,14 +878,14 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="14">
-        <v>-100</v>
+      <c r="L14" s="15">
+        <v>0</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="14">
-        <v>-100</v>
+      <c r="N14" s="15">
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,37 +895,37 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="15">
-        <v>3</v>
-      </c>
-      <c r="H15" s="14">
+      <c r="G15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15" s="15">
         <v>-100</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="14">
         <v>1</v>
       </c>
-      <c r="J15" s="15">
-        <v>3</v>
-      </c>
-      <c r="K15" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="L15" s="14">
+      <c r="J15" s="14">
+        <v>4</v>
+      </c>
+      <c r="K15" s="15">
+        <v>-75</v>
+      </c>
+      <c r="L15" s="15">
         <v>-50</v>
       </c>
-      <c r="M15" s="14">
+      <c r="M15" s="15">
         <v>-50</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="15">
         <v>-66.666666666666</v>
       </c>
     </row>
@@ -933,205 +933,205 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="15">
+      <c r="E16" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F16" s="14">
         <v>8</v>
       </c>
-      <c r="G16" s="15">
-        <v>3</v>
-      </c>
-      <c r="H16" s="14">
-        <v>166.666666666667</v>
-      </c>
-      <c r="I16" s="15">
-        <v>14</v>
-      </c>
-      <c r="J16" s="15">
+      <c r="G16" s="14">
         <v>5</v>
       </c>
-      <c r="K16" s="14">
-        <v>180</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-12.5</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-26.315789473684</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-74.545454545454</v>
+      <c r="H16" s="15">
+        <v>60</v>
+      </c>
+      <c r="I16" s="14">
+        <v>15</v>
+      </c>
+      <c r="J16" s="14">
+        <v>7</v>
+      </c>
+      <c r="K16" s="15">
+        <v>114.285714285714</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-11.764705882352</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-31.818181818181</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-76.923076923076</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>6</v>
-      </c>
-      <c r="D17" s="15">
-        <v>2</v>
-      </c>
-      <c r="E17" s="14">
-        <v>200</v>
-      </c>
-      <c r="F17" s="15">
+      <c r="C17" s="14">
+        <v>4</v>
+      </c>
+      <c r="D17" s="14">
+        <v>4</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14">
         <v>26</v>
       </c>
-      <c r="G17" s="15">
-        <v>20</v>
-      </c>
-      <c r="H17" s="14">
-        <v>30</v>
-      </c>
-      <c r="I17" s="15">
-        <v>43</v>
-      </c>
-      <c r="J17" s="15">
-        <v>28</v>
-      </c>
-      <c r="K17" s="14">
-        <v>53.571428571428</v>
-      </c>
-      <c r="L17" s="14">
-        <v>48.275862068965</v>
-      </c>
-      <c r="M17" s="14">
-        <v>152.941176470588</v>
-      </c>
-      <c r="N17" s="14">
-        <v>0</v>
+      <c r="G17" s="14">
+        <v>15</v>
+      </c>
+      <c r="H17" s="15">
+        <v>73.333333333333</v>
+      </c>
+      <c r="I17" s="14">
+        <v>48</v>
+      </c>
+      <c r="J17" s="14">
+        <v>32</v>
+      </c>
+      <c r="K17" s="15">
+        <v>50</v>
+      </c>
+      <c r="L17" s="15">
+        <v>37.142857142857</v>
+      </c>
+      <c r="M17" s="15">
+        <v>152.631578947368</v>
+      </c>
+      <c r="N17" s="15">
+        <v>-7.692307692307</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="15">
-        <v>2</v>
-      </c>
-      <c r="G18" s="15">
-        <v>2</v>
-      </c>
-      <c r="H18" s="14">
+      <c r="E18" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="14">
+        <v>1</v>
+      </c>
+      <c r="G18" s="14">
+        <v>3</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I18" s="14">
+        <v>4</v>
+      </c>
+      <c r="J18" s="14">
+        <v>4</v>
+      </c>
+      <c r="K18" s="15">
         <v>0</v>
       </c>
-      <c r="I18" s="15">
-        <v>4</v>
-      </c>
-      <c r="J18" s="15">
-        <v>3</v>
-      </c>
-      <c r="K18" s="14">
-        <v>33.333333333333</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-75</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-93.220338983050</v>
+      <c r="L18" s="15">
+        <v>-63.636363636363</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-76.470588235294</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-93.846153846153</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="15">
+      <c r="C19" s="14">
         <v>3</v>
       </c>
-      <c r="E19" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F19" s="15">
-        <v>9</v>
-      </c>
-      <c r="G19" s="15">
+      <c r="D19" s="14">
+        <v>4</v>
+      </c>
+      <c r="E19" s="15">
+        <v>-25</v>
+      </c>
+      <c r="F19" s="14">
         <v>7</v>
       </c>
-      <c r="H19" s="14">
-        <v>28.571428571428</v>
-      </c>
-      <c r="I19" s="15">
-        <v>10</v>
-      </c>
-      <c r="J19" s="15">
-        <v>15</v>
-      </c>
-      <c r="K19" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="M19" s="14">
-        <v>25</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-66.666666666666</v>
+      <c r="G19" s="14">
+        <v>8</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-12.5</v>
+      </c>
+      <c r="I19" s="14">
+        <v>13</v>
+      </c>
+      <c r="J19" s="14">
+        <v>19</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-31.578947368421</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-35</v>
+      </c>
+      <c r="M19" s="15">
+        <v>30</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-63.888888888888</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="15">
+      <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="E20" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F20" s="15">
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="14">
         <v>2</v>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="14">
         <v>2</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="15">
         <v>0</v>
       </c>
-      <c r="I20" s="15">
-        <v>2</v>
-      </c>
-      <c r="J20" s="15">
+      <c r="I20" s="14">
         <v>3</v>
       </c>
-      <c r="K20" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="L20" s="14">
+      <c r="J20" s="14">
+        <v>3</v>
+      </c>
+      <c r="K20" s="15">
+        <v>0</v>
+      </c>
+      <c r="L20" s="15">
         <v>-50</v>
       </c>
-      <c r="M20" s="14">
-        <v>-85.714285714285</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-96.428571428571</v>
+      <c r="M20" s="15">
+        <v>-81.25</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-95.081967213114</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>9</v>
       </c>
       <c r="D21" s="17">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>50</v>
+        <v>-25</v>
       </c>
       <c r="F21" s="17">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G21" s="17">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H21" s="18">
-        <v>27.027027027027</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I21" s="17">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="J21" s="17">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="K21" s="18">
-        <v>29.824561403508</v>
+        <v>23.188405797101</v>
       </c>
       <c r="L21" s="18">
-        <v>1.369863013698</v>
+        <v>-7.608695652173</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.631578947368</v>
+        <v>-1.162790697674</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.161290322580</v>
+        <v>-70.175438596491</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,29 +1188,29 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="14">
         <v>2</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="15">
-        <v>2</v>
-      </c>
       <c r="J22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="K22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L22" s="14">
+      <c r="L22" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="M22" s="13" t="s">
-        <v>21</v>
+      <c r="M22" s="15">
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,34 +1223,34 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="15">
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="14">
+        <v>5</v>
+      </c>
+      <c r="G23" s="14">
         <v>6</v>
       </c>
-      <c r="G23" s="15">
-        <v>5</v>
-      </c>
-      <c r="H23" s="14">
-        <v>20</v>
-      </c>
-      <c r="I23" s="15">
+      <c r="H23" s="15">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="I23" s="14">
         <v>9</v>
       </c>
-      <c r="J23" s="15">
-        <v>6</v>
-      </c>
-      <c r="K23" s="14">
-        <v>50</v>
-      </c>
-      <c r="L23" s="14">
+      <c r="J23" s="14">
+        <v>8</v>
+      </c>
+      <c r="K23" s="15">
         <v>12.5</v>
       </c>
-      <c r="M23" s="14">
+      <c r="L23" s="15">
+        <v>-10</v>
+      </c>
+      <c r="M23" s="15">
         <v>28.571428571428</v>
       </c>
       <c r="N23" s="13" t="s">
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>20</v>
-      </c>
-      <c r="D24" s="15">
-        <v>13</v>
-      </c>
-      <c r="E24" s="14">
-        <v>53.846153846153</v>
-      </c>
-      <c r="F24" s="15">
-        <v>69</v>
-      </c>
-      <c r="G24" s="15">
-        <v>59</v>
-      </c>
-      <c r="H24" s="14">
-        <v>16.949152542372</v>
-      </c>
-      <c r="I24" s="15">
-        <v>93</v>
-      </c>
-      <c r="J24" s="15">
+      <c r="C24" s="14">
+        <v>23</v>
+      </c>
+      <c r="D24" s="14">
+        <v>10</v>
+      </c>
+      <c r="E24" s="15">
+        <v>130</v>
+      </c>
+      <c r="F24" s="14">
         <v>71</v>
       </c>
-      <c r="K24" s="14">
-        <v>30.985915492957</v>
-      </c>
-      <c r="L24" s="14">
-        <v>50</v>
-      </c>
-      <c r="M24" s="14">
-        <v>111.363636363636</v>
+      <c r="G24" s="14">
+        <v>54</v>
+      </c>
+      <c r="H24" s="15">
+        <v>31.481481481481</v>
+      </c>
+      <c r="I24" s="14">
+        <v>116</v>
+      </c>
+      <c r="J24" s="14">
+        <v>81</v>
+      </c>
+      <c r="K24" s="15">
+        <v>43.209876543209</v>
+      </c>
+      <c r="L24" s="15">
+        <v>48.717948717948</v>
+      </c>
+      <c r="M24" s="15">
+        <v>141.666666666667</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="14">
+        <v>4</v>
+      </c>
+      <c r="D25" s="14">
         <v>1</v>
       </c>
-      <c r="D25" s="15">
-        <v>2</v>
-      </c>
-      <c r="E25" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F25" s="15">
-        <v>10</v>
-      </c>
-      <c r="G25" s="15">
+      <c r="E25" s="15">
+        <v>300</v>
+      </c>
+      <c r="F25" s="14">
+        <v>9</v>
+      </c>
+      <c r="G25" s="14">
         <v>7</v>
       </c>
-      <c r="H25" s="14">
-        <v>42.857142857142</v>
-      </c>
-      <c r="I25" s="15">
-        <v>15</v>
-      </c>
-      <c r="J25" s="15">
-        <v>7</v>
-      </c>
-      <c r="K25" s="14">
-        <v>114.285714285714</v>
-      </c>
-      <c r="L25" s="14">
+      <c r="H25" s="15">
+        <v>28.571428571428</v>
+      </c>
+      <c r="I25" s="14">
+        <v>20</v>
+      </c>
+      <c r="J25" s="14">
+        <v>8</v>
+      </c>
+      <c r="K25" s="15">
         <v>150</v>
+      </c>
+      <c r="L25" s="15">
+        <v>233.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>13</v>
-      </c>
-      <c r="D26" s="15">
-        <v>9</v>
-      </c>
-      <c r="E26" s="14">
-        <v>44.444444444444</v>
-      </c>
-      <c r="F26" s="15">
-        <v>35</v>
-      </c>
-      <c r="G26" s="15">
-        <v>30</v>
-      </c>
-      <c r="H26" s="14">
-        <v>16.666666666666</v>
-      </c>
-      <c r="I26" s="15">
-        <v>46</v>
-      </c>
-      <c r="J26" s="15">
-        <v>43</v>
-      </c>
-      <c r="K26" s="14">
-        <v>6.976744186046</v>
-      </c>
-      <c r="L26" s="14">
-        <v>-4.166666666666</v>
-      </c>
-      <c r="M26" s="14">
-        <v>4.545454545454</v>
+      <c r="C26" s="14">
+        <v>6</v>
+      </c>
+      <c r="D26" s="14">
+        <v>11</v>
+      </c>
+      <c r="E26" s="15">
+        <v>-45.454545454545</v>
+      </c>
+      <c r="F26" s="14">
+        <v>29</v>
+      </c>
+      <c r="G26" s="14">
+        <v>34</v>
+      </c>
+      <c r="H26" s="15">
+        <v>-14.705882352941</v>
+      </c>
+      <c r="I26" s="14">
+        <v>51</v>
+      </c>
+      <c r="J26" s="14">
+        <v>54</v>
+      </c>
+      <c r="K26" s="15">
+        <v>-5.555555555555</v>
+      </c>
+      <c r="L26" s="15">
+        <v>-3.773584905660</v>
+      </c>
+      <c r="M26" s="15">
+        <v>2</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,31 +1387,31 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="14">
         <v>3</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="14">
         <v>2</v>
       </c>
-      <c r="J27" s="15">
-        <v>3</v>
-      </c>
-      <c r="K27" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="L27" s="14">
+      <c r="J27" s="14">
+        <v>5</v>
+      </c>
+      <c r="K27" s="15">
+        <v>-60</v>
+      </c>
+      <c r="L27" s="15">
         <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
-      </c>
-      <c r="D28" s="15">
+      <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="E28" s="14">
-        <v>100</v>
-      </c>
-      <c r="F28" s="15">
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
         <v>4</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="14">
         <v>1</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="15">
         <v>300</v>
       </c>
-      <c r="I28" s="15">
-        <v>6</v>
-      </c>
-      <c r="J28" s="15">
+      <c r="I28" s="14">
+        <v>7</v>
+      </c>
+      <c r="J28" s="14">
         <v>3</v>
       </c>
-      <c r="K28" s="14">
-        <v>100</v>
-      </c>
-      <c r="L28" s="14">
-        <v>20</v>
+      <c r="K28" s="15">
+        <v>133.333333333333</v>
+      </c>
+      <c r="L28" s="15">
+        <v>40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="15">
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="15">
-        <v>1</v>
-      </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="14">
+      <c r="L29" s="15">
         <v>0</v>
       </c>
-      <c r="M29" s="14">
+      <c r="M29" s="15">
         <v>-50</v>
       </c>
-      <c r="N29" s="14">
-        <v>-83.333333333333</v>
+      <c r="N29" s="15">
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="15">
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="15">
-        <v>1</v>
-      </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="14">
+      <c r="L30" s="15">
         <v>0</v>
       </c>
-      <c r="M30" s="14">
+      <c r="M30" s="15">
         <v>-50</v>
       </c>
-      <c r="N30" s="14">
-        <v>-83.333333333333</v>
+      <c r="N30" s="15">
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>14</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>16</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>9</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>6</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>4</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>-55.555555555555</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-75</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-71.428571428571</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>67</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>42</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>32</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>17</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>35</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>105.882352941176</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>9.375</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-16.666666666666</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>-47.761194029850</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>826</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>710</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>413</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>247</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>102</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-58.704453441295</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-75.302663438256</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-85.633802816901</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-87.651331719128</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>588</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>524</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>418</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>301</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>386</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>28.239202657807</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>-7.655502392344</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-26.335877862595</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>-34.353741496598</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>825</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>768</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>370</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>216</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>77</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-64.351851851851</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-79.189189189189</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-89.973958333333</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-90.666666666666</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>362</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>330</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>203</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>189</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>191</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>1.058201058201</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>-5.911330049261</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-42.121212121212</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-47.237569060773</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>719</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>460</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>184</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>158</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>41</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-74.050632911392</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-77.717391304347</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-91.086956521739</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-94.297635605007</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-101pct.xlsx
+++ b/data/source/weekly/cs-en-us-101pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>0</v>
       </c>
       <c r="L14" s="15">
         <v>0</v>
@@ -914,19 +914,19 @@
         <v>1</v>
       </c>
       <c r="J15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="L15" s="15">
         <v>-50</v>
       </c>
       <c r="M15" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>2</v>
+      </c>
+      <c r="D16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
         <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="I16" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K16" s="15">
-        <v>114.285714285714</v>
+        <v>112.5</v>
       </c>
       <c r="L16" s="15">
-        <v>-11.764705882352</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M16" s="15">
-        <v>-31.818181818181</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="N16" s="15">
-        <v>-76.923076923076</v>
+        <v>-78.205128205128</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G17" s="14">
         <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>73.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J17" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K17" s="15">
-        <v>50</v>
+        <v>48.571428571428</v>
       </c>
       <c r="L17" s="15">
-        <v>37.142857142857</v>
+        <v>26.829268292682</v>
       </c>
       <c r="M17" s="15">
-        <v>152.631578947368</v>
+        <v>173.684210526316</v>
       </c>
       <c r="N17" s="15">
-        <v>-7.692307692307</v>
+        <v>-11.864406779661</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1028,28 +1028,28 @@
         <v>1</v>
       </c>
       <c r="G18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
         <v>4</v>
       </c>
       <c r="J18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L18" s="15">
         <v>-63.636363636363</v>
       </c>
       <c r="M18" s="15">
-        <v>-76.470588235294</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.846153846153</v>
+        <v>-94.520547945205</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>400</v>
       </c>
       <c r="F19" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G19" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H19" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J19" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K19" s="15">
-        <v>-31.578947368421</v>
+        <v>-10</v>
       </c>
       <c r="L19" s="15">
-        <v>-35</v>
+        <v>-28</v>
       </c>
       <c r="M19" s="15">
-        <v>30</v>
+        <v>63.636363636363</v>
       </c>
       <c r="N19" s="15">
-        <v>-63.888888888888</v>
+        <v>-57.142857142857</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1110,28 +1110,28 @@
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" s="14">
         <v>3</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-50</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M20" s="15">
-        <v>-81.25</v>
+        <v>-76.470588235294</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.081967213114</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="F21" s="17">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G21" s="17">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H21" s="18">
-        <v>28.571428571428</v>
+        <v>20.588235294117</v>
       </c>
       <c r="I21" s="17">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="J21" s="17">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="K21" s="18">
-        <v>23.188405797101</v>
+        <v>25.974025974026</v>
       </c>
       <c r="L21" s="18">
-        <v>-7.608695652173</v>
+        <v>-10.185185185185</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.162790697674</v>
+        <v>6.593406593406</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.175438596491</v>
+        <v>-70.336391437308</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="14">
+      <c r="C23" s="14">
         <v>2</v>
       </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-16.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="I23" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J23" s="14">
         <v>8</v>
       </c>
       <c r="K23" s="15">
-        <v>12.5</v>
+        <v>37.5</v>
       </c>
       <c r="L23" s="15">
-        <v>-10</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M23" s="15">
-        <v>28.571428571428</v>
+        <v>57.142857142857</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>130</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="F24" s="14">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G24" s="14">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H24" s="15">
-        <v>31.481481481481</v>
+        <v>21.052631578947</v>
       </c>
       <c r="I24" s="14">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="J24" s="14">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="K24" s="15">
-        <v>43.209876543209</v>
+        <v>33</v>
       </c>
       <c r="L24" s="15">
-        <v>48.717948717948</v>
+        <v>47.777777777777</v>
       </c>
       <c r="M24" s="15">
-        <v>141.666666666667</v>
+        <v>155.769230769231</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>300</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G25" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H25" s="15">
-        <v>28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J25" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K25" s="15">
-        <v>150</v>
+        <v>90.909090909090</v>
       </c>
       <c r="L25" s="15">
-        <v>233.333333333333</v>
+        <v>250</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-45.454545454545</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G26" s="14">
         <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>-14.705882352941</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="I26" s="14">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J26" s="14">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.555555555555</v>
+        <v>-4.838709677419</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.773584905660</v>
+        <v>3.508771929824</v>
       </c>
       <c r="M26" s="15">
-        <v>2</v>
+        <v>7.272727272727</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
         <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
         <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K28" s="15">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="L28" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-101pct.xlsx
+++ b/data/source/weekly/cs-en-us-101pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -860,23 +860,23 @@
       <c r="E14" s="15">
         <v>-100</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L14" s="15">
         <v>0</v>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -923,10 +923,10 @@
         <v>-50</v>
       </c>
       <c r="M15" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N15" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>100</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J16" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K16" s="15">
-        <v>112.5</v>
+        <v>72.727272727272</v>
       </c>
       <c r="L16" s="15">
-        <v>-19.047619047619</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="M16" s="15">
-        <v>-26.086956521739</v>
+        <v>-24</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.205128205128</v>
+        <v>-78.409090909090</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>33.333333333333</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F17" s="14">
         <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>33.333333333333</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I17" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J17" s="14">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K17" s="15">
-        <v>48.571428571428</v>
+        <v>29.545454545454</v>
       </c>
       <c r="L17" s="15">
-        <v>26.829268292682</v>
+        <v>18.75</v>
       </c>
       <c r="M17" s="15">
-        <v>173.684210526316</v>
+        <v>159.090909090909</v>
       </c>
       <c r="N17" s="15">
-        <v>-11.864406779661</v>
+        <v>-10.9375</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K18" s="15">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>-63.636363636363</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="M18" s="15">
-        <v>-77.777777777777</v>
+        <v>-77.272727272727</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.520547945205</v>
+        <v>-93.670886075949</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>400</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G19" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J19" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K19" s="15">
-        <v>-10</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>-28</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="M19" s="15">
-        <v>63.636363636363</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>-57.142857142857</v>
+        <v>-52.380952380952</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1125,13 +1125,13 @@
         <v>33.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-42.857142857142</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M20" s="15">
         <v>-76.470588235294</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.117647058823</v>
+        <v>-95.061728395061</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>50</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="F21" s="17">
         <v>41</v>
       </c>
       <c r="G21" s="17">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H21" s="18">
-        <v>20.588235294117</v>
+        <v>-6.818181818181</v>
       </c>
       <c r="I21" s="17">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="J21" s="17">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="K21" s="18">
-        <v>25.974025974026</v>
+        <v>12.631578947368</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.185185185185</v>
+        <v>-14.4</v>
       </c>
       <c r="M21" s="18">
-        <v>6.593406593406</v>
+        <v>4.901960784313</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.336391437308</v>
+        <v>-70.441988950276</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,34 +1221,34 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="15">
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
         <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
         <v>11</v>
       </c>
       <c r="J23" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K23" s="15">
-        <v>37.5</v>
+        <v>10</v>
       </c>
       <c r="L23" s="15">
-        <v>-15.384615384615</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M23" s="15">
         <v>57.142857142857</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>-10.526315789473</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F24" s="14">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G24" s="14">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H24" s="15">
-        <v>21.052631578947</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I24" s="14">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="J24" s="14">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="K24" s="15">
-        <v>33</v>
+        <v>26.548672566371</v>
       </c>
       <c r="L24" s="15">
-        <v>47.777777777777</v>
+        <v>36.190476190476</v>
       </c>
       <c r="M24" s="15">
-        <v>155.769230769231</v>
+        <v>160</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,10 +1306,10 @@
         <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
         <v>8</v>
@@ -1321,16 +1321,16 @@
         <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J25" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K25" s="15">
-        <v>90.909090909090</v>
+        <v>69.230769230769</v>
       </c>
       <c r="L25" s="15">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F26" s="14">
         <v>31</v>
       </c>
       <c r="G26" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.823529411764</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="I26" s="14">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J26" s="14">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.838709677419</v>
+        <v>-9.859154929577</v>
       </c>
       <c r="L26" s="15">
-        <v>3.508771929824</v>
+        <v>3.225806451612</v>
       </c>
       <c r="M26" s="15">
-        <v>7.272727272727</v>
+        <v>4.918032786885</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
-      </c>
-      <c r="F27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27" s="14">
         <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28" s="15">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-101pct.xlsx
+++ b/data/source/weekly/cs-en-us-101pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="15">
+        <v>-75</v>
+      </c>
+      <c r="I15" s="14">
         <v>2</v>
       </c>
-      <c r="H15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I15" s="14">
-        <v>1</v>
-      </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>-80</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L15" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="M15" s="15">
         <v>-50</v>
       </c>
-      <c r="M15" s="15">
-        <v>-75</v>
-      </c>
       <c r="N15" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="14">
-        <v>3</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>1</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
         <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" s="14">
         <v>11</v>
       </c>
       <c r="K16" s="15">
-        <v>72.727272727272</v>
+        <v>81.818181818181</v>
       </c>
       <c r="L16" s="15">
-        <v>-17.391304347826</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M16" s="15">
-        <v>-24</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.409090909090</v>
+        <v>-79.797979797979</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>-44.444444444444</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F17" s="14">
         <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>11.111111111111</v>
+        <v>-25.925925925925</v>
       </c>
       <c r="I17" s="14">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J17" s="14">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="K17" s="15">
-        <v>29.545454545454</v>
+        <v>16.363636363636</v>
       </c>
       <c r="L17" s="15">
-        <v>18.75</v>
+        <v>10.344827586206</v>
       </c>
       <c r="M17" s="15">
-        <v>159.090909090909</v>
+        <v>146.153846153846</v>
       </c>
       <c r="N17" s="15">
-        <v>-10.9375</v>
+        <v>-9.859154929577</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="14">
         <v>5</v>
       </c>
       <c r="J18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L18" s="15">
-        <v>-61.538461538461</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="M18" s="15">
-        <v>-77.272727272727</v>
+        <v>-79.166666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.670886075949</v>
+        <v>-94.252873563218</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>-60</v>
       </c>
       <c r="F19" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G19" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H19" s="15">
-        <v>-16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I19" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J19" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.666666666666</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="L19" s="15">
-        <v>-31.034482758620</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="M19" s="15">
-        <v>66.666666666666</v>
+        <v>22.222222222222</v>
       </c>
       <c r="N19" s="15">
-        <v>-52.380952380952</v>
+        <v>-53.191489361702</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
         <v>1</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I20" s="14">
+        <v>6</v>
+      </c>
+      <c r="J20" s="14">
         <v>4</v>
       </c>
-      <c r="J20" s="14">
-        <v>3</v>
-      </c>
       <c r="K20" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="L20" s="15">
-        <v>-55.555555555555</v>
+        <v>-40</v>
       </c>
       <c r="M20" s="15">
-        <v>-76.470588235294</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.061728395061</v>
+        <v>-93.258426966292</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-38.888888888888</v>
+        <v>-45</v>
       </c>
       <c r="F21" s="17">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G21" s="17">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.818181818181</v>
+        <v>-25.862068965517</v>
       </c>
       <c r="I21" s="17">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="J21" s="17">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="K21" s="18">
-        <v>12.631578947368</v>
+        <v>4.347826086956</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.4</v>
+        <v>-16.083916083916</v>
       </c>
       <c r="M21" s="18">
-        <v>4.901960784313</v>
+        <v>1.694915254237</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.441988950276</v>
+        <v>-70.074812967581</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,32 +1182,32 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>2</v>
       </c>
-      <c r="J22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>21</v>
+      <c r="J22" s="14">
+        <v>1</v>
+      </c>
+      <c r="K22" s="15">
+        <v>100</v>
       </c>
       <c r="L22" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M22" s="15">
         <v>0</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="I23" s="14">
+        <v>13</v>
+      </c>
+      <c r="J23" s="14">
         <v>11</v>
       </c>
-      <c r="J23" s="14">
-        <v>10</v>
-      </c>
       <c r="K23" s="15">
-        <v>10</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L23" s="15">
-        <v>-21.428571428571</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M23" s="15">
-        <v>57.142857142857</v>
+        <v>44.444444444444</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>-30.769230769230</v>
+        <v>20</v>
       </c>
       <c r="F24" s="14">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G24" s="14">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H24" s="15">
-        <v>27.272727272727</v>
+        <v>19.298245614035</v>
       </c>
       <c r="I24" s="14">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="J24" s="14">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="K24" s="15">
-        <v>26.548672566371</v>
+        <v>25.78125</v>
       </c>
       <c r="L24" s="15">
-        <v>36.190476190476</v>
+        <v>41.228070175438</v>
       </c>
       <c r="M24" s="15">
-        <v>160</v>
+        <v>177.586206896552</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,10 +1303,10 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
         <v>-50</v>
@@ -1315,22 +1315,22 @@
         <v>8</v>
       </c>
       <c r="G25" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I25" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J25" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K25" s="15">
-        <v>69.230769230769</v>
+        <v>41.176470588235</v>
       </c>
       <c r="L25" s="15">
-        <v>175</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-44.444444444444</v>
+        <v>37.5</v>
       </c>
       <c r="F26" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H26" s="15">
-        <v>-16.216216216216</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="J26" s="14">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.859154929577</v>
+        <v>-5.063291139240</v>
       </c>
       <c r="L26" s="15">
-        <v>3.225806451612</v>
+        <v>11.940298507462</v>
       </c>
       <c r="M26" s="15">
-        <v>4.918032786885</v>
+        <v>7.142857142857</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F27" s="14">
+        <v>1</v>
       </c>
       <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-80</v>
+      </c>
+      <c r="I27" s="14">
         <v>3</v>
       </c>
-      <c r="H27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I27" s="14">
-        <v>2</v>
-      </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>-66.666666666666</v>
+        <v>-62.5</v>
       </c>
       <c r="L27" s="15">
         <v>0</v>
@@ -1425,23 +1425,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>2</v>
+      </c>
+      <c r="G28" s="14">
+        <v>2</v>
+      </c>
+      <c r="H28" s="15">
         <v>0</v>
-      </c>
-      <c r="F28" s="14">
-        <v>4</v>
-      </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
-      <c r="H28" s="15">
-        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
         <v>8</v>
@@ -1453,7 +1453,7 @@
         <v>60</v>
       </c>
       <c r="L28" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.888888888888</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.888888888888</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-101pct.xlsx
+++ b/data/source/weekly/cs-en-us-101pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="E15" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="14">
         <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>-71.428571428571</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L15" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="M15" s="15">
+        <v>-25</v>
+      </c>
+      <c r="N15" s="15">
         <v>-50</v>
-      </c>
-      <c r="N15" s="15">
-        <v>-60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D16" s="14">
+        <v>2</v>
+      </c>
+      <c r="E16" s="15">
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
         <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I16" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J16" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K16" s="15">
-        <v>81.818181818181</v>
+        <v>84.615384615384</v>
       </c>
       <c r="L16" s="15">
-        <v>-23.076923076923</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M16" s="15">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.797979797979</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
         <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>-45.454545454545</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F17" s="14">
         <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H17" s="15">
-        <v>-25.925925925925</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="I17" s="14">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J17" s="14">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="K17" s="15">
-        <v>16.363636363636</v>
+        <v>3.030303030303</v>
       </c>
       <c r="L17" s="15">
-        <v>10.344827586206</v>
+        <v>7.936507936507</v>
       </c>
       <c r="M17" s="15">
-        <v>146.153846153846</v>
+        <v>112.5</v>
       </c>
       <c r="N17" s="15">
-        <v>-9.859154929577</v>
+        <v>-16.049382716049</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>-75</v>
+        <v>-40</v>
       </c>
       <c r="I18" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J18" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K18" s="15">
-        <v>-28.571428571428</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L18" s="15">
-        <v>-64.285714285714</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="M18" s="15">
-        <v>-79.166666666666</v>
+        <v>-72</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.252873563218</v>
+        <v>-93</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,13 +1057,13 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>-60</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
         <v>12</v>
@@ -1075,22 +1075,22 @@
         <v>-14.285714285714</v>
       </c>
       <c r="I19" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J19" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K19" s="15">
-        <v>-24.137931034482</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="L19" s="15">
-        <v>-29.032258064516</v>
+        <v>-21.875</v>
       </c>
       <c r="M19" s="15">
-        <v>22.222222222222</v>
+        <v>25</v>
       </c>
       <c r="N19" s="15">
-        <v>-53.191489361702</v>
+        <v>-51.923076923076</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1110,28 +1110,28 @@
         <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L20" s="15">
-        <v>-40</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M20" s="15">
-        <v>-66.666666666666</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.258426966292</v>
+        <v>-92.708333333333</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
         <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-45</v>
+        <v>-25</v>
       </c>
       <c r="F21" s="17">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G21" s="17">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.862068965517</v>
+        <v>-25.757575757575</v>
       </c>
       <c r="I21" s="17">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="J21" s="17">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="K21" s="18">
-        <v>4.347826086956</v>
+        <v>0</v>
       </c>
       <c r="L21" s="18">
-        <v>-16.083916083916</v>
+        <v>-14.012738853503</v>
       </c>
       <c r="M21" s="18">
-        <v>1.694915254237</v>
+        <v>2.272727272727</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.074812967581</v>
+        <v>-69.730941704035</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
         <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
+        <v>14</v>
+      </c>
+      <c r="J23" s="14">
         <v>13</v>
       </c>
-      <c r="J23" s="14">
-        <v>11</v>
-      </c>
       <c r="K23" s="15">
-        <v>18.181818181818</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L23" s="15">
-        <v>-7.142857142857</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="M23" s="15">
-        <v>44.444444444444</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E24" s="15">
-        <v>20</v>
+        <v>157.142857142857</v>
       </c>
       <c r="F24" s="14">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G24" s="14">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H24" s="15">
-        <v>19.298245614035</v>
+        <v>14.814814814814</v>
       </c>
       <c r="I24" s="14">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="J24" s="14">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K24" s="15">
-        <v>25.78125</v>
+        <v>31.851851851851</v>
       </c>
       <c r="L24" s="15">
-        <v>41.228070175438</v>
+        <v>39.0625</v>
       </c>
       <c r="M24" s="15">
-        <v>177.586206896552</v>
+        <v>182.539682539683</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
-      </c>
-      <c r="D25" s="14">
-        <v>4</v>
-      </c>
-      <c r="E25" s="15">
-        <v>-50</v>
+        <v>3</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G25" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H25" s="15">
-        <v>-20</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I25" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J25" s="14">
         <v>17</v>
       </c>
       <c r="K25" s="15">
-        <v>41.176470588235</v>
+        <v>58.823529411764</v>
       </c>
       <c r="L25" s="15">
-        <v>166.666666666667</v>
+        <v>200</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>8</v>
+      </c>
+      <c r="D26" s="14">
         <v>11</v>
       </c>
-      <c r="D26" s="14">
-        <v>8</v>
-      </c>
       <c r="E26" s="15">
-        <v>37.5</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G26" s="14">
         <v>36</v>
       </c>
       <c r="H26" s="15">
-        <v>-16.666666666666</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="J26" s="14">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.063291139240</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L26" s="15">
-        <v>11.940298507462</v>
+        <v>10.526315789473</v>
       </c>
       <c r="M26" s="15">
-        <v>7.142857142857</v>
+        <v>13.513513513513</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>2</v>
       </c>
-      <c r="E27" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F27" s="14">
-        <v>1</v>
-      </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-80</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
         <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,13 +1435,13 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
         <v>8</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
         <v>-90.909090909090</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
         <v>-90.909090909090</v>

--- a/data/source/weekly/cs-en-us-101pct.xlsx
+++ b/data/source/weekly/cs-en-us-101pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -864,7 +864,7 @@
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -881,11 +881,11 @@
       <c r="L14" s="15">
         <v>0</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
+        <v>-25</v>
+      </c>
+      <c r="I15" s="14">
+        <v>4</v>
+      </c>
+      <c r="J15" s="14">
+        <v>9</v>
+      </c>
+      <c r="K15" s="15">
+        <v>-55.555555555555</v>
+      </c>
+      <c r="L15" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="I15" s="14">
-        <v>3</v>
-      </c>
-      <c r="J15" s="14">
-        <v>7</v>
-      </c>
-      <c r="K15" s="15">
-        <v>-57.142857142857</v>
-      </c>
-      <c r="L15" s="15">
-        <v>-25</v>
-      </c>
       <c r="M15" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,10 +934,10 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
         <v>100</v>
@@ -952,22 +952,22 @@
         <v>50</v>
       </c>
       <c r="I16" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J16" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="15">
-        <v>84.615384615384</v>
+        <v>92.857142857142</v>
       </c>
       <c r="L16" s="15">
-        <v>-11.111111111111</v>
+        <v>-10</v>
       </c>
       <c r="M16" s="15">
-        <v>-25</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.777777777777</v>
+        <v>-77.685950413223</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-63.636363636363</v>
+        <v>12.5</v>
       </c>
       <c r="F17" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H17" s="15">
-        <v>-41.176470588235</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="I17" s="14">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="J17" s="14">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K17" s="15">
-        <v>3.030303030303</v>
+        <v>6.756756756756</v>
       </c>
       <c r="L17" s="15">
-        <v>7.936507936507</v>
+        <v>9.722222222222</v>
       </c>
       <c r="M17" s="15">
-        <v>112.5</v>
+        <v>113.513513513514</v>
       </c>
       <c r="N17" s="15">
-        <v>-16.049382716049</v>
+        <v>-11.235955056179</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J18" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K18" s="15">
-        <v>-22.222222222222</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L18" s="15">
-        <v>-58.823529411764</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M18" s="15">
-        <v>-72</v>
+        <v>-68</v>
       </c>
       <c r="N18" s="15">
-        <v>-93</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="F19" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G19" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H19" s="15">
-        <v>-14.285714285714</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J19" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K19" s="15">
-        <v>-24.242424242424</v>
+        <v>-20</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.875</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="M19" s="15">
-        <v>25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>-51.923076923076</v>
+        <v>-52.542372881355</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1110,28 +1110,28 @@
         <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K20" s="15">
-        <v>40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-46.153846153846</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M20" s="15">
-        <v>-63.157894736842</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.708333333333</v>
+        <v>-92.727272727272</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>6.25</v>
       </c>
       <c r="F21" s="17">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G21" s="17">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.757575757575</v>
+        <v>-27.027027027027</v>
       </c>
       <c r="I21" s="17">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="J21" s="17">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="K21" s="18">
-        <v>0</v>
+        <v>2.649006622516</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.012738853503</v>
+        <v>-10.919540229885</v>
       </c>
       <c r="M21" s="18">
-        <v>2.272727272727</v>
+        <v>9.154929577464</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.730941704035</v>
+        <v>-69.061876247505</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I23" s="14">
         <v>14</v>
       </c>
       <c r="J23" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K23" s="15">
-        <v>7.692307692307</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L23" s="15">
-        <v>-17.647058823529</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M23" s="15">
         <v>16.666666666666</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E24" s="15">
-        <v>157.142857142857</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F24" s="14">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G24" s="14">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H24" s="15">
-        <v>14.814814814814</v>
+        <v>22.448979591836</v>
       </c>
       <c r="I24" s="14">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="J24" s="14">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="K24" s="15">
-        <v>31.851851851851</v>
+        <v>30.201342281879</v>
       </c>
       <c r="L24" s="15">
-        <v>39.0625</v>
+        <v>43.703703703703</v>
       </c>
       <c r="M24" s="15">
-        <v>182.539682539683</v>
+        <v>181.159420289855</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D25" s="14">
+        <v>4</v>
+      </c>
+      <c r="E25" s="15">
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G25" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H25" s="15">
-        <v>-22.222222222222</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J25" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K25" s="15">
-        <v>58.823529411764</v>
+        <v>47.619047619047</v>
       </c>
       <c r="L25" s="15">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>-27.272727272727</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H26" s="15">
+        <v>-11.764705882352</v>
+      </c>
+      <c r="I26" s="14">
+        <v>88</v>
+      </c>
+      <c r="J26" s="14">
+        <v>96</v>
+      </c>
+      <c r="K26" s="15">
         <v>-8.333333333333</v>
       </c>
-      <c r="I26" s="14">
-        <v>84</v>
-      </c>
-      <c r="J26" s="14">
-        <v>90</v>
-      </c>
-      <c r="K26" s="15">
-        <v>-6.666666666666</v>
-      </c>
       <c r="L26" s="15">
-        <v>10.526315789473</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M26" s="15">
-        <v>13.513513513513</v>
+        <v>11.392405063291</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="L27" s="15">
-        <v>-20</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>4</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
         <v>1</v>
       </c>
-      <c r="G28" s="14">
-        <v>2</v>
-      </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>400</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
         <v>5</v>
       </c>
       <c r="K28" s="15">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-101pct.xlsx
+++ b/data/source/weekly/cs-en-us-101pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -879,7 +879,7 @@
         <v>-50</v>
       </c>
       <c r="L14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M14" s="15">
         <v>0</v>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-50</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
@@ -920,7 +920,7 @@
         <v>-55.555555555555</v>
       </c>
       <c r="L15" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M15" s="15">
         <v>0</v>
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
         <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J16" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K16" s="15">
-        <v>92.857142857142</v>
+        <v>76.470588235294</v>
       </c>
       <c r="L16" s="15">
-        <v>-10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M16" s="15">
-        <v>-18.181818181818</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.685950413223</v>
+        <v>-78.260869565217</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>12.5</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F17" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G17" s="14">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H17" s="15">
-        <v>-35.897435897435</v>
+        <v>-37.837837837837</v>
       </c>
       <c r="I17" s="14">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J17" s="14">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="K17" s="15">
-        <v>6.756756756756</v>
+        <v>2.469135802469</v>
       </c>
       <c r="L17" s="15">
-        <v>9.722222222222</v>
+        <v>7.792207792207</v>
       </c>
       <c r="M17" s="15">
-        <v>113.513513513514</v>
+        <v>102.439024390244</v>
       </c>
       <c r="N17" s="15">
-        <v>-11.235955056179</v>
+        <v>-13.541666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1028,28 +1028,28 @@
         <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J18" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K18" s="15">
-        <v>-27.272727272727</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="L18" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="M18" s="15">
-        <v>-68</v>
+        <v>-64</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.857142857142</v>
+        <v>-92.913385826771</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,10 +1060,10 @@
         <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>50</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
         <v>10</v>
@@ -1075,22 +1075,22 @@
         <v>-33.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J19" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K19" s="15">
-        <v>-20</v>
+        <v>-20.512820512820</v>
       </c>
       <c r="L19" s="15">
-        <v>-15.151515151515</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="M19" s="15">
-        <v>33.333333333333</v>
+        <v>34.782608695652</v>
       </c>
       <c r="N19" s="15">
-        <v>-52.542372881355</v>
+        <v>-50.793650793650</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
         <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
         <v>0</v>
       </c>
       <c r="I20" s="14">
+        <v>10</v>
+      </c>
+      <c r="J20" s="14">
         <v>8</v>
       </c>
-      <c r="J20" s="14">
-        <v>6</v>
-      </c>
       <c r="K20" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="L20" s="15">
-        <v>-42.857142857142</v>
+        <v>-37.5</v>
       </c>
       <c r="M20" s="15">
-        <v>-61.904761904761</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.727272727272</v>
+        <v>-91.735537190082</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>6.25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G21" s="17">
         <v>74</v>
       </c>
       <c r="H21" s="18">
-        <v>-27.027027027027</v>
+        <v>-25.675675675675</v>
       </c>
       <c r="I21" s="17">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="J21" s="17">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="K21" s="18">
-        <v>2.649006622516</v>
+        <v>-0.591715976331</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.919540229885</v>
+        <v>-11.578947368421</v>
       </c>
       <c r="M21" s="18">
-        <v>9.154929577464</v>
+        <v>10.526315789473</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.061876247505</v>
+        <v>-69.729729729729</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
         <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K23" s="15">
-        <v>-17.647058823529</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>-26.315789473684</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M23" s="15">
-        <v>16.666666666666</v>
+        <v>25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G24" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H24" s="15">
-        <v>22.448979591836</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I24" s="14">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="J24" s="14">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="K24" s="15">
-        <v>30.201342281879</v>
+        <v>26.785714285714</v>
       </c>
       <c r="L24" s="15">
-        <v>43.703703703703</v>
+        <v>48.951048951049</v>
       </c>
       <c r="M24" s="15">
-        <v>181.159420289855</v>
+        <v>195.833333333333</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
         <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" s="14">
         <v>10</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I25" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J25" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K25" s="15">
-        <v>47.619047619047</v>
+        <v>43.478260869565</v>
       </c>
       <c r="L25" s="15">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>-16.666666666666</v>
+        <v>10</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G26" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H26" s="15">
-        <v>-11.764705882352</v>
+        <v>2.857142857142</v>
       </c>
       <c r="I26" s="14">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J26" s="14">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="K26" s="15">
-        <v>-8.333333333333</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="L26" s="15">
-        <v>14.285714285714</v>
+        <v>13.636363636363</v>
       </c>
       <c r="M26" s="15">
-        <v>11.392405063291</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>4</v>
@@ -1412,7 +1412,7 @@
         <v>-40</v>
       </c>
       <c r="L27" s="15">
-        <v>-14.285714285714</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
         <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28" s="15">
-        <v>140</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,10 +1494,10 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="N29" s="15">
         <v>-91.666666666666</v>
@@ -1535,10 +1535,10 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="15">
         <v>-91.666666666666</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1575,8 +1575,8 @@
       <c r="K31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-101pct.xlsx
+++ b/data/source/weekly/cs-en-us-101pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -882,7 +882,7 @@
         <v>-50</v>
       </c>
       <c r="M14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N14" s="15">
         <v>-75</v>
@@ -895,32 +895,32 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
         <v>3</v>
       </c>
-      <c r="G15" s="14">
-        <v>4</v>
-      </c>
       <c r="H15" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
+        <v>-60</v>
+      </c>
+      <c r="L15" s="15">
         <v>-55.555555555555</v>
-      </c>
-      <c r="L15" s="15">
-        <v>-42.857142857142</v>
       </c>
       <c r="M15" s="15">
         <v>0</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="14">
-        <v>3</v>
-      </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="I16" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J16" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K16" s="15">
-        <v>76.470588235294</v>
+        <v>63.157894736842</v>
       </c>
       <c r="L16" s="15">
-        <v>-9.090909090909</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="M16" s="15">
-        <v>-16.666666666666</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.260869565217</v>
+        <v>-79.194630872483</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
         <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>-42.857142857142</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G17" s="14">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H17" s="15">
-        <v>-37.837837837837</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="I17" s="14">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J17" s="14">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="K17" s="15">
-        <v>2.469135802469</v>
+        <v>5.681818181818</v>
       </c>
       <c r="L17" s="15">
-        <v>7.792207792207</v>
+        <v>12.048192771084</v>
       </c>
       <c r="M17" s="15">
-        <v>102.439024390244</v>
+        <v>121.428571428571</v>
       </c>
       <c r="N17" s="15">
-        <v>-13.541666666666</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>-42.857142857142</v>
+        <v>-25</v>
       </c>
       <c r="I18" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J18" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K18" s="15">
-        <v>-30.769230769230</v>
+        <v>-20</v>
       </c>
       <c r="L18" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-64</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.913385826771</v>
+        <v>-92.356687898089</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>600</v>
       </c>
       <c r="F19" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G19" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H19" s="15">
-        <v>-33.333333333333</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I19" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J19" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K19" s="15">
-        <v>-20.512820512820</v>
+        <v>-5</v>
       </c>
       <c r="L19" s="15">
-        <v>-16.216216216216</v>
+        <v>-5</v>
       </c>
       <c r="M19" s="15">
-        <v>34.782608695652</v>
+        <v>52</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.793650793650</v>
+        <v>-43.283582089552</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
         <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
         <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I20" s="14">
         <v>10</v>
       </c>
       <c r="J20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="15">
-        <v>25</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L20" s="15">
-        <v>-37.5</v>
+        <v>-50</v>
       </c>
       <c r="M20" s="15">
         <v>-54.545454545454</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.735537190082</v>
+        <v>-92.537313432835</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>-33.333333333333</v>
+        <v>21.428571428571</v>
       </c>
       <c r="F21" s="17">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G21" s="17">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.675675675675</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="I21" s="17">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="J21" s="17">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.591715976331</v>
+        <v>3.278688524590</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.578947368421</v>
+        <v>-8.252427184466</v>
       </c>
       <c r="M21" s="18">
-        <v>10.526315789473</v>
+        <v>18.867924528301</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.729729729729</v>
+        <v>-69.367909238249</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>2</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
         <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I23" s="14">
         <v>15</v>
       </c>
       <c r="J23" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K23" s="15">
-        <v>-16.666666666666</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="L23" s="15">
-        <v>-28.571428571428</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="M23" s="15">
-        <v>25</v>
+        <v>15.384615384615</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F24" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G24" s="14">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="H24" s="15">
-        <v>27.272727272727</v>
+        <v>50</v>
       </c>
       <c r="I24" s="14">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="J24" s="14">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="K24" s="15">
-        <v>26.785714285714</v>
+        <v>30.337078651685</v>
       </c>
       <c r="L24" s="15">
-        <v>48.951048951049</v>
+        <v>44.099378881987</v>
       </c>
       <c r="M24" s="15">
-        <v>195.833333333333</v>
+        <v>201.298701298701</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
-      </c>
-      <c r="D25" s="14">
-        <v>2</v>
-      </c>
-      <c r="E25" s="15">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H25" s="15">
-        <v>10</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J25" s="14">
         <v>23</v>
       </c>
       <c r="K25" s="15">
-        <v>43.478260869565</v>
+        <v>47.826086956521</v>
       </c>
       <c r="L25" s="15">
-        <v>230</v>
+        <v>209.090909090909</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>10</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G26" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H26" s="15">
-        <v>2.857142857142</v>
+        <v>-20.512820512820</v>
       </c>
       <c r="I26" s="14">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="J26" s="14">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.660377358490</v>
+        <v>-11.016949152542</v>
       </c>
       <c r="L26" s="15">
-        <v>13.636363636363</v>
+        <v>12.903225806451</v>
       </c>
       <c r="M26" s="15">
-        <v>11.111111111111</v>
+        <v>8.247422680412</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,17 +1387,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
         <v>0</v>
@@ -1406,13 +1406,13 @@
         <v>6</v>
       </c>
       <c r="J27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>-40</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
         <v>14</v>
       </c>
       <c r="J28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28" s="15">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="L28" s="15">
-        <v>75</v>
+        <v>55.555555555555</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,7 +1485,7 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1494,21 +1494,21 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.666666666666</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,7 +1526,7 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1535,13 +1535,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-91.666666666666</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-101pct.xlsx
+++ b/data/source/weekly/cs-en-us-101pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -882,7 +882,7 @@
         <v>-50</v>
       </c>
       <c r="M14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
         <v>-75</v>
@@ -902,22 +902,22 @@
         <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>-60</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="L15" s="15">
         <v>-55.555555555555</v>
@@ -937,37 +937,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="F16" s="14">
+        <v>7</v>
+      </c>
+      <c r="G16" s="14">
         <v>10</v>
       </c>
-      <c r="G16" s="14">
-        <v>8</v>
-      </c>
       <c r="H16" s="15">
-        <v>25</v>
+        <v>-30</v>
       </c>
       <c r="I16" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J16" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K16" s="15">
-        <v>63.157894736842</v>
+        <v>39.130434782608</v>
       </c>
       <c r="L16" s="15">
-        <v>-8.823529411764</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="M16" s="15">
-        <v>-16.216216216216</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.194630872483</v>
+        <v>-79.746835443038</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F17" s="14">
+        <v>30</v>
+      </c>
+      <c r="G17" s="14">
         <v>26</v>
       </c>
-      <c r="G17" s="14">
-        <v>33</v>
-      </c>
       <c r="H17" s="15">
-        <v>-21.212121212121</v>
+        <v>15.384615384615</v>
       </c>
       <c r="I17" s="14">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J17" s="14">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K17" s="15">
-        <v>5.681818181818</v>
+        <v>9.782608695652</v>
       </c>
       <c r="L17" s="15">
-        <v>12.048192771084</v>
+        <v>12.222222222222</v>
       </c>
       <c r="M17" s="15">
-        <v>121.428571428571</v>
+        <v>124.444444444444</v>
       </c>
       <c r="N17" s="15">
-        <v>-7</v>
+        <v>-4.716981132075</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-25</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J18" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" s="15">
-        <v>-20</v>
+        <v>-18.75</v>
       </c>
       <c r="L18" s="15">
-        <v>-33.333333333333</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="M18" s="15">
-        <v>-55.555555555555</v>
+        <v>-55.172413793103</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.356687898089</v>
+        <v>-92.613636363636</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,72 +1057,72 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D19" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
-        <v>600</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G19" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H19" s="15">
-        <v>27.272727272727</v>
+        <v>20</v>
       </c>
       <c r="I19" s="14">
         <v>38</v>
       </c>
       <c r="J19" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K19" s="15">
-        <v>-5</v>
+        <v>-11.627906976744</v>
       </c>
       <c r="L19" s="15">
-        <v>-5</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M19" s="15">
         <v>52</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.283582089552</v>
+        <v>-47.945205479452</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H20" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
         <v>10</v>
       </c>
       <c r="J20" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K20" s="15">
-        <v>11.111111111111</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L20" s="15">
         <v>-50</v>
@@ -1131,7 +1131,7 @@
         <v>-54.545454545454</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.537313432835</v>
+        <v>-93.055555555555</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>21.428571428571</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G21" s="17">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.823529411764</v>
+        <v>-6.349206349206</v>
       </c>
       <c r="I21" s="17">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="J21" s="17">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="K21" s="18">
-        <v>3.278688524590</v>
+        <v>0.505050505050</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.252427184466</v>
+        <v>-9.132420091324</v>
       </c>
       <c r="M21" s="18">
-        <v>18.867924528301</v>
+        <v>19.879518072289</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.367909238249</v>
+        <v>-70.164917541229</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="14">
         <v>1</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L22" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="C23" s="14">
+        <v>3</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>-75</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I23" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J23" s="14">
         <v>19</v>
       </c>
       <c r="K23" s="15">
-        <v>-21.052631578947</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-34.782608695652</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="M23" s="15">
-        <v>15.384615384615</v>
+        <v>46.153846153846</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>110</v>
+        <v>23.529411764705</v>
       </c>
       <c r="F24" s="14">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G24" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H24" s="15">
-        <v>50</v>
+        <v>31.666666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="J24" s="14">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="K24" s="15">
-        <v>30.337078651685</v>
+        <v>30.256410256410</v>
       </c>
       <c r="L24" s="15">
-        <v>44.099378881987</v>
+        <v>47.674418604651</v>
       </c>
       <c r="M24" s="15">
-        <v>201.298701298701</v>
+        <v>195.348837209302</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D25" s="14">
+        <v>5</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-40</v>
       </c>
       <c r="F25" s="14">
         <v>10</v>
       </c>
       <c r="G25" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H25" s="15">
-        <v>66.666666666666</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I25" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J25" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K25" s="15">
-        <v>47.826086956521</v>
+        <v>32.142857142857</v>
       </c>
       <c r="L25" s="15">
-        <v>209.090909090909</v>
+        <v>236.363636363636</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-41.666666666666</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F26" s="14">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G26" s="14">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H26" s="15">
-        <v>-20.512820512820</v>
+        <v>-21.621621621621</v>
       </c>
       <c r="I26" s="14">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="J26" s="14">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="K26" s="15">
-        <v>-11.016949152542</v>
+        <v>-12.598425196850</v>
       </c>
       <c r="L26" s="15">
-        <v>12.903225806451</v>
+        <v>9.900990099009</v>
       </c>
       <c r="M26" s="15">
-        <v>8.247422680412</v>
+        <v>7.766990291262</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,22 +1394,22 @@
         <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>6</v>
       </c>
       <c r="J27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>-45.454545454545</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="15">
         <v>-45.454545454545</v>
@@ -1438,22 +1438,22 @@
         <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
         <v>14</v>
       </c>
       <c r="J28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L28" s="15">
-        <v>55.555555555555</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1494,7 +1494,7 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
         <v>-66.666666666666</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1535,7 +1535,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M30" s="15">
         <v>-66.666666666666</v>

--- a/data/source/weekly/cs-en-us-101pct.xlsx
+++ b/data/source/weekly/cs-en-us-101pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,82 +892,82 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>-63.636363636363</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="L15" s="15">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N15" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
+        <v>3</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F16" s="14">
         <v>4</v>
       </c>
-      <c r="E16" s="15">
-        <v>-75</v>
-      </c>
-      <c r="F16" s="14">
-        <v>7</v>
-      </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>-30</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I16" s="14">
         <v>32</v>
       </c>
       <c r="J16" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K16" s="15">
-        <v>39.130434782608</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L16" s="15">
-        <v>-8.571428571428</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M16" s="15">
         <v>-15.789473684210</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.746835443038</v>
+        <v>-81.395348837209</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>15.384615384615</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J17" s="14">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K17" s="15">
-        <v>9.782608695652</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L17" s="15">
-        <v>12.222222222222</v>
+        <v>2.941176470588</v>
       </c>
       <c r="M17" s="15">
-        <v>124.444444444444</v>
+        <v>118.75</v>
       </c>
       <c r="N17" s="15">
-        <v>-4.716981132075</v>
+        <v>-6.25</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>-28.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="14">
         <v>13</v>
       </c>
       <c r="J18" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K18" s="15">
-        <v>-18.75</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="L18" s="15">
-        <v>-31.578947368421</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="M18" s="15">
-        <v>-55.172413793103</v>
+        <v>-58.064516129032</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.613636363636</v>
+        <v>-93.264248704663</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G19" s="14">
         <v>10</v>
       </c>
       <c r="H19" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I19" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J19" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.627906976744</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.636363636363</v>
+        <v>-10.638297872340</v>
       </c>
       <c r="M19" s="15">
-        <v>52</v>
+        <v>61.538461538461</v>
       </c>
       <c r="N19" s="15">
-        <v>-47.945205479452</v>
+        <v>-46.153846153846</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,20 +1100,20 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="I20" s="14">
         <v>10</v>
@@ -1125,13 +1125,13 @@
         <v>-9.090909090909</v>
       </c>
       <c r="L20" s="15">
-        <v>-50</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M20" s="15">
-        <v>-54.545454545454</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.055555555555</v>
+        <v>-93.975903614457</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>-33.333333333333</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F21" s="17">
+        <v>50</v>
+      </c>
+      <c r="G21" s="17">
         <v>59</v>
       </c>
-      <c r="G21" s="17">
-        <v>63</v>
-      </c>
       <c r="H21" s="18">
-        <v>-6.349206349206</v>
+        <v>-15.254237288135</v>
       </c>
       <c r="I21" s="17">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="J21" s="17">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="K21" s="18">
-        <v>0.505050505050</v>
+        <v>-0.952380952380</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.132420091324</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M21" s="18">
-        <v>19.879518072289</v>
+        <v>20.231213872832</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.164917541229</v>
+        <v>-71.545827633378</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="14">
         <v>1</v>
       </c>
       <c r="K22" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L22" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>100</v>
+      </c>
+      <c r="F23" s="14">
+        <v>6</v>
+      </c>
+      <c r="G23" s="14">
         <v>3</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="14">
-        <v>5</v>
-      </c>
-      <c r="G23" s="14">
-        <v>6</v>
-      </c>
       <c r="H23" s="15">
-        <v>-16.666666666666</v>
+        <v>100</v>
       </c>
       <c r="I23" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J23" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K23" s="15">
         <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-20.833333333333</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M23" s="15">
-        <v>46.153846153846</v>
+        <v>53.846153846153</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>23.529411764705</v>
+        <v>73.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G24" s="14">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H24" s="15">
-        <v>31.666666666666</v>
+        <v>42.622950819672</v>
       </c>
       <c r="I24" s="14">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="J24" s="14">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="K24" s="15">
-        <v>30.256410256410</v>
+        <v>32.857142857142</v>
       </c>
       <c r="L24" s="15">
-        <v>47.674418604651</v>
+        <v>55</v>
       </c>
       <c r="M24" s="15">
-        <v>195.348837209302</v>
+        <v>184.69387755102</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
+        <v>-62.5</v>
+      </c>
+      <c r="F25" s="14">
+        <v>9</v>
+      </c>
+      <c r="G25" s="14">
+        <v>15</v>
+      </c>
+      <c r="H25" s="15">
         <v>-40</v>
       </c>
-      <c r="F25" s="14">
-        <v>10</v>
-      </c>
-      <c r="G25" s="14">
-        <v>11</v>
-      </c>
-      <c r="H25" s="15">
-        <v>-9.090909090909</v>
-      </c>
       <c r="I25" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J25" s="14">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="K25" s="15">
-        <v>32.142857142857</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L25" s="15">
-        <v>236.363636363636</v>
+        <v>233.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-22.222222222222</v>
+        <v>25</v>
       </c>
       <c r="F26" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G26" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H26" s="15">
-        <v>-21.621621621621</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="I26" s="14">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="J26" s="14">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="K26" s="15">
-        <v>-12.598425196850</v>
+        <v>-10.370370370370</v>
       </c>
       <c r="L26" s="15">
-        <v>9.900990099009</v>
+        <v>4.310344827586</v>
       </c>
       <c r="M26" s="15">
-        <v>7.766990291262</v>
+        <v>7.079646017699</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="C27" s="14">
+        <v>3</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="14">
-        <v>4</v>
-      </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
         <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="L27" s="15">
-        <v>-45.454545454545</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
+      <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J28" s="14">
         <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="L28" s="15">
-        <v>27.272727272727</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M29" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-83.333333333333</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,13 +1535,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M30" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-83.333333333333</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-101pct.xlsx
+++ b/data/source/weekly/cs-en-us-101pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -870,30 +870,30 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="14">
         <v>2</v>
       </c>
       <c r="K14" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L14" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N14" s="15">
-        <v>-75</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -923,51 +923,51 @@
         <v>-50</v>
       </c>
       <c r="M15" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
         <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-66.666666666666</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I16" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J16" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K16" s="15">
-        <v>23.076923076923</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L16" s="15">
-        <v>-11.111111111111</v>
+        <v>-8.108108108108</v>
       </c>
       <c r="M16" s="15">
-        <v>-15.789473684210</v>
+        <v>-17.073170731707</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.395348837209</v>
+        <v>-81.318681318681</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J17" s="14">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="K17" s="15">
-        <v>7.142857142857</v>
+        <v>-0.900900900900</v>
       </c>
       <c r="L17" s="15">
-        <v>2.941176470588</v>
+        <v>1.851851851851</v>
       </c>
       <c r="M17" s="15">
-        <v>118.75</v>
+        <v>115.686274509804</v>
       </c>
       <c r="N17" s="15">
-        <v>-6.25</v>
+        <v>-10.569105691056</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
+        <v>-57.142857142857</v>
+      </c>
+      <c r="I18" s="14">
+        <v>14</v>
+      </c>
+      <c r="J18" s="14">
+        <v>20</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-30</v>
+      </c>
+      <c r="L18" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="I18" s="14">
-        <v>13</v>
-      </c>
-      <c r="J18" s="14">
-        <v>17</v>
-      </c>
-      <c r="K18" s="15">
-        <v>-23.529411764705</v>
-      </c>
-      <c r="L18" s="15">
-        <v>-38.095238095238</v>
-      </c>
       <c r="M18" s="15">
-        <v>-58.064516129032</v>
+        <v>-56.25</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.264248704663</v>
+        <v>-93.488372093023</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
         <v>14</v>
       </c>
       <c r="G19" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H19" s="15">
-        <v>40</v>
+        <v>55.555555555555</v>
       </c>
       <c r="I19" s="14">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J19" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K19" s="15">
-        <v>-6.666666666666</v>
+        <v>-2.083333333333</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.638297872340</v>
+        <v>-2.083333333333</v>
       </c>
       <c r="M19" s="15">
-        <v>61.538461538461</v>
+        <v>62.068965517241</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.153846153846</v>
+        <v>-44.047619047619</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>-40</v>
+        <v>-75</v>
       </c>
       <c r="I20" s="14">
         <v>10</v>
       </c>
       <c r="J20" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K20" s="15">
-        <v>-9.090909090909</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-54.545454545454</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="M20" s="15">
-        <v>-56.521739130434</v>
+        <v>-60</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.975903614457</v>
+        <v>-94.350282485875</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-8.333333333333</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F21" s="17">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G21" s="17">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.254237288135</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I21" s="17">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="J21" s="17">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.952380952380</v>
+        <v>-4.310344827586</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.333333333333</v>
+        <v>-10.843373493975</v>
       </c>
       <c r="M21" s="18">
-        <v>20.231213872832</v>
+        <v>19.354838709677</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.545827633378</v>
+        <v>-72.005044136191</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
         <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I23" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J23" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>4.761904761904</v>
       </c>
       <c r="L23" s="15">
-        <v>-23.076923076923</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="M23" s="15">
-        <v>53.846153846153</v>
+        <v>57.142857142857</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>73.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F24" s="14">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G24" s="14">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H24" s="15">
-        <v>42.622950819672</v>
+        <v>50.793650793650</v>
       </c>
       <c r="I24" s="14">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="J24" s="14">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="K24" s="15">
-        <v>32.857142857142</v>
+        <v>32.467532467532</v>
       </c>
       <c r="L24" s="15">
-        <v>55</v>
+        <v>61.052631578947</v>
       </c>
       <c r="M24" s="15">
-        <v>184.69387755102</v>
+        <v>191.428571428571</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>-62.5</v>
+        <v>400</v>
       </c>
       <c r="F25" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H25" s="15">
-        <v>-40</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I25" s="14">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J25" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K25" s="15">
-        <v>11.111111111111</v>
+        <v>24.324324324324</v>
       </c>
       <c r="L25" s="15">
-        <v>233.333333333333</v>
+        <v>228.571428571429</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>25</v>
+        <v>-75</v>
       </c>
       <c r="F26" s="14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G26" s="14">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H26" s="15">
-        <v>-12.820512820512</v>
+        <v>-35.555555555555</v>
       </c>
       <c r="I26" s="14">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J26" s="14">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.370370370370</v>
+        <v>-17.218543046357</v>
       </c>
       <c r="L26" s="15">
-        <v>4.310344827586</v>
+        <v>1.626016260162</v>
       </c>
       <c r="M26" s="15">
-        <v>7.079646017699</v>
+        <v>3.305785123966</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>3</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>9</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>-25</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="L27" s="15">
         <v>-30.769230769230</v>
@@ -1425,23 +1425,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="14">
-        <v>3</v>
-      </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
         <v>15</v>
@@ -1453,7 +1453,7 @@
         <v>87.5</v>
       </c>
       <c r="L28" s="15">
-        <v>36.363636363636</v>
+        <v>25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>100</v>
       </c>
       <c r="L29" s="15">
         <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N29" s="15">
-        <v>-84.615384615384</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>100</v>
       </c>
       <c r="L30" s="15">
         <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N30" s="15">
-        <v>-84.615384615384</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-101pct.xlsx
+++ b/data/source/weekly/cs-en-us-101pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -914,16 +914,16 @@
         <v>5</v>
       </c>
       <c r="J15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>-54.545454545454</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="L15" s="15">
         <v>-50</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N15" s="15">
         <v>-28.571428571428</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
         <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H16" s="15">
-        <v>-63.636363636363</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I16" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J16" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>21.428571428571</v>
+        <v>21.875</v>
       </c>
       <c r="L16" s="15">
-        <v>-8.108108108108</v>
+        <v>2.631578947368</v>
       </c>
       <c r="M16" s="15">
-        <v>-17.073170731707</v>
+        <v>-11.363636363636</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.318681318681</v>
+        <v>-79.365079365079</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>-84.615384615384</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G17" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H17" s="15">
-        <v>-26.666666666666</v>
+        <v>-43.75</v>
       </c>
       <c r="I17" s="14">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="J17" s="14">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="K17" s="15">
-        <v>-0.900900900900</v>
+        <v>-5.833333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>1.851851851851</v>
+        <v>-1.739130434782</v>
       </c>
       <c r="M17" s="15">
-        <v>115.686274509804</v>
+        <v>105.454545454545</v>
       </c>
       <c r="N17" s="15">
-        <v>-10.569105691056</v>
+        <v>-12.403100775193</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
         <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-57.142857142857</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J18" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K18" s="15">
-        <v>-30</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L18" s="15">
-        <v>-33.333333333333</v>
+        <v>-36</v>
       </c>
       <c r="M18" s="15">
-        <v>-56.25</v>
+        <v>-54.285714285714</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.488372093023</v>
+        <v>-93.162393162393</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F19" s="14">
+        <v>10</v>
+      </c>
+      <c r="G19" s="14">
         <v>14</v>
       </c>
-      <c r="G19" s="14">
-        <v>9</v>
-      </c>
       <c r="H19" s="15">
-        <v>55.555555555555</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I19" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J19" s="14">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K19" s="15">
-        <v>-2.083333333333</v>
+        <v>-9.259259259259</v>
       </c>
       <c r="L19" s="15">
-        <v>-2.083333333333</v>
+        <v>-2</v>
       </c>
       <c r="M19" s="15">
-        <v>62.068965517241</v>
+        <v>63.333333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.047619047619</v>
+        <v>-44.943820224719</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>-75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J20" s="14">
         <v>12</v>
       </c>
       <c r="K20" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-56.521739130434</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="M20" s="15">
-        <v>-60</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.350282485875</v>
+        <v>-93.582887700534</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
         <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-63.636363636363</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="F21" s="17">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G21" s="17">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.571428571428</v>
+        <v>-39.436619718309</v>
       </c>
       <c r="I21" s="17">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="J21" s="17">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.310344827586</v>
+        <v>-7.086614173228</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.843373493975</v>
+        <v>-10.266159695817</v>
       </c>
       <c r="M21" s="18">
-        <v>19.354838709677</v>
+        <v>18</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.005044136191</v>
+        <v>-71.904761904761</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>66.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I23" s="14">
         <v>22</v>
       </c>
       <c r="J23" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K23" s="15">
-        <v>4.761904761904</v>
+        <v>-12</v>
       </c>
       <c r="L23" s="15">
-        <v>-18.518518518518</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M23" s="15">
-        <v>57.142857142857</v>
+        <v>37.5</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E24" s="15">
-        <v>28.571428571428</v>
+        <v>175</v>
       </c>
       <c r="F24" s="14">
         <v>95</v>
       </c>
       <c r="G24" s="14">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H24" s="15">
-        <v>50.793650793650</v>
+        <v>55.737704918032</v>
       </c>
       <c r="I24" s="14">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="J24" s="14">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="K24" s="15">
-        <v>32.467532467532</v>
+        <v>37.238493723849</v>
       </c>
       <c r="L24" s="15">
-        <v>61.052631578947</v>
+        <v>62.376237623762</v>
       </c>
       <c r="M24" s="15">
-        <v>191.428571428571</v>
+        <v>180.34188034188</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>400</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G25" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H25" s="15">
-        <v>-7.142857142857</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J25" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K25" s="15">
-        <v>24.324324324324</v>
+        <v>27.5</v>
       </c>
       <c r="L25" s="15">
-        <v>228.571428571429</v>
+        <v>218.75</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>-75</v>
+        <v>-30</v>
       </c>
       <c r="F26" s="14">
         <v>29</v>
       </c>
       <c r="G26" s="14">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>-35.555555555555</v>
+        <v>-32.558139534883</v>
       </c>
       <c r="I26" s="14">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="J26" s="14">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="K26" s="15">
-        <v>-17.218543046357</v>
+        <v>-18.012422360248</v>
       </c>
       <c r="L26" s="15">
-        <v>1.626016260162</v>
+        <v>3.937007874015</v>
       </c>
       <c r="M26" s="15">
-        <v>3.305785123966</v>
+        <v>1.538461538461</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1406,10 +1406,10 @@
         <v>9</v>
       </c>
       <c r="J27" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" s="15">
-        <v>-30.769230769230</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L27" s="15">
         <v>-30.769230769230</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>87.5</v>
+        <v>40</v>
       </c>
       <c r="L28" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,20 +1469,20 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
@@ -1497,10 +1497,10 @@
         <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
       <c r="N29" s="15">
-        <v>-85.714285714285</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,20 +1510,20 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
@@ -1538,10 +1538,10 @@
         <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-85.714285714285</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-101pct.xlsx
+++ b/data/source/weekly/cs-en-us-101pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -882,10 +882,10 @@
         <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -914,10 +914,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K15" s="15">
-        <v>-58.333333333333</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="L15" s="15">
         <v>-50</v>
@@ -926,7 +926,7 @@
         <v>-16.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
         <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>-38.461538461538</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J16" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K16" s="15">
-        <v>21.875</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L16" s="15">
-        <v>2.631578947368</v>
+        <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-11.363636363636</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-79.365079365079</v>
+        <v>-79.591836734693</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>-66.666666666666</v>
+        <v>-10</v>
       </c>
       <c r="F17" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H17" s="15">
-        <v>-43.75</v>
+        <v>-44.736842105263</v>
       </c>
       <c r="I17" s="14">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="J17" s="14">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.833333333333</v>
+        <v>-6.153846153846</v>
       </c>
       <c r="L17" s="15">
-        <v>-1.739130434782</v>
+        <v>2.521008403361</v>
       </c>
       <c r="M17" s="15">
-        <v>105.454545454545</v>
+        <v>103.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-12.403100775193</v>
+        <v>-14.084507042253</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
         <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I18" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K18" s="15">
-        <v>-27.272727272727</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="L18" s="15">
-        <v>-36</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-54.285714285714</v>
+        <v>-51.351351351351</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.162393162393</v>
+        <v>-92.653061224489</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G19" s="14">
         <v>14</v>
       </c>
       <c r="H19" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I19" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J19" s="14">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K19" s="15">
-        <v>-9.259259259259</v>
+        <v>-8.771929824561</v>
       </c>
       <c r="L19" s="15">
-        <v>-2</v>
+        <v>-5.454545454545</v>
       </c>
       <c r="M19" s="15">
-        <v>63.333333333333</v>
+        <v>52.941176470588</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.943820224719</v>
+        <v>-49.019607843137</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
         <v>12</v>
       </c>
       <c r="J20" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L20" s="15">
-        <v>-47.826086956521</v>
+        <v>-50</v>
       </c>
       <c r="M20" s="15">
         <v>-55.555555555555</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.582887700534</v>
+        <v>-93.877551020408</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-40.909090909090</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="F21" s="17">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G21" s="17">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H21" s="18">
-        <v>-39.436619718309</v>
+        <v>-34.666666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="J21" s="17">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.086614173228</v>
+        <v>-8.058608058608</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.266159695817</v>
+        <v>-9.386281588447</v>
       </c>
       <c r="M21" s="18">
-        <v>18</v>
+        <v>16.203703703703</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.904761904761</v>
+        <v>-71.955307262569</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>300</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M22" s="15">
         <v>33.333333333333</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F23" s="14">
         <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H23" s="15">
-        <v>-16.666666666666</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I23" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J23" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K23" s="15">
-        <v>-12</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L23" s="15">
-        <v>-21.428571428571</v>
+        <v>-20</v>
       </c>
       <c r="M23" s="15">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>175</v>
+        <v>23.529411764705</v>
       </c>
       <c r="F24" s="14">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G24" s="14">
         <v>61</v>
       </c>
       <c r="H24" s="15">
-        <v>55.737704918032</v>
+        <v>57.377049180327</v>
       </c>
       <c r="I24" s="14">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="J24" s="14">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="K24" s="15">
-        <v>37.238493723849</v>
+        <v>36.328125</v>
       </c>
       <c r="L24" s="15">
-        <v>62.376237623762</v>
+        <v>63.849765258216</v>
       </c>
       <c r="M24" s="15">
-        <v>180.34188034188</v>
+        <v>176.984126984127</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>66.666666666666</v>
+        <v>300</v>
       </c>
       <c r="F25" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G25" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>38.461538461538</v>
       </c>
       <c r="I25" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J25" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K25" s="15">
-        <v>27.5</v>
+        <v>34.146341463414</v>
       </c>
       <c r="L25" s="15">
-        <v>218.75</v>
+        <v>223.529411764706</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H26" s="15">
-        <v>-32.558139534883</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="I26" s="14">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="J26" s="14">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="K26" s="15">
-        <v>-18.012422360248</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L26" s="15">
-        <v>3.937007874015</v>
+        <v>2.941176470588</v>
       </c>
       <c r="M26" s="15">
-        <v>1.538461538461</v>
+        <v>-2.097902097902</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1406,13 +1406,13 @@
         <v>9</v>
       </c>
       <c r="J27" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K27" s="15">
+        <v>-40</v>
+      </c>
+      <c r="L27" s="15">
         <v>-35.714285714285</v>
-      </c>
-      <c r="L27" s="15">
-        <v>-30.769230769230</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,7 +1429,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
@@ -1447,10 +1447,10 @@
         <v>14</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>40</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L28" s="15">
         <v>0</v>
@@ -1469,17 +1469,17 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>2</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1488,19 +1488,19 @@
         <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L29" s="15">
         <v>-50</v>
       </c>
       <c r="M29" s="15">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N29" s="15">
-        <v>-86.666666666666</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,17 +1510,17 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1529,19 +1529,19 @@
         <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
         <v>-50</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N30" s="15">
-        <v>-86.666666666666</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="31" spans="1:14">
